--- a/backend/models/SAM_221.xlsx
+++ b/backend/models/SAM_221.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alqer\Desktop\Kaizen\EcoKaizen\Dr.Houyam_sessions\excercise\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alqer\Desktop\Kaizen\EcoKaizen\ecokaizen_alpha\backend\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1E6C53-3EDA-4206-8340-4FFC32D06DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C36C979-D686-440B-BF7E-4012A8986BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SAM_221" sheetId="2" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,9 +78,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,10 +389,22 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>5.1639777946687895</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>2.5819888975751533</v>
       </c>
     </row>
@@ -400,10 +412,22 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
         <v>5.163977794772924</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>7.745966693799744</v>
       </c>
     </row>
@@ -411,107 +435,93 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>3.8729833464134442</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>6.4549722443686885</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>3.872983345830499</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>6.4549722408318235</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
         <v>2.581988897695533</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>7.7459666899967425</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
         <v>7.7459666930865989</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>2.5819888966655808</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
